--- a/public/informes-templates/INFORME ADICIONAL  .xlsx
+++ b/public/informes-templates/INFORME ADICIONAL  .xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{234C05B2-A289-4074-BAF0-3DCFF57F4287}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{514FD4D7-833F-4AA4-80C5-64B7042E906B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,36 +15,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="29">
-  <si>
-    <t>INFORME DE SERVICIO</t>
-  </si>
-  <si>
-    <t>EMPRESA / CLIENTE</t>
-  </si>
-  <si>
-    <t>CONTACTO</t>
-  </si>
-  <si>
-    <t>ORDEN DE COMPRA</t>
-  </si>
-  <si>
-    <t>COT</t>
-  </si>
-  <si>
-    <t>LINEA / AREA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DESCRIPCION </t>
-  </si>
-  <si>
-    <t>TIPO</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
   <si>
     <t>CANTIDAD</t>
-  </si>
-  <si>
-    <t>FECHA</t>
   </si>
   <si>
     <t>DATOS DEL COMPONENTE</t>
@@ -103,12 +76,18 @@
   <si>
     <t>RECOMENDACIONES</t>
   </si>
+  <si>
+    <t>DESCRIPCION</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -131,13 +110,6 @@
       <i/>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <sz val="8"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -175,7 +147,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -197,6 +169,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.499984740745262"/>
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
@@ -345,7 +329,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -353,29 +337,35 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -383,91 +373,79 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -485,55 +463,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -737,23 +666,23 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Z182"/>
+  <dimension ref="A1:Z174"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="8" width="18.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
-        <v>0</v>
+      <c r="A1" s="24" t="s">
+        <v>20</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="12"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="14"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -774,14 +703,14 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="13"/>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="15"/>
+      <c r="A2" s="26"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="28"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -802,18 +731,15 @@
       <c r="Z2" s="1"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="16"/>
-      <c r="B3" s="12"/>
-      <c r="C3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="19"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="12"/>
+      <c r="A3" s="25"/>
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="30"/>
       <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
@@ -832,16 +758,14 @@
       <c r="Z3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="17"/>
-      <c r="B4" s="18"/>
-      <c r="C4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="19"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="12"/>
+      <c r="A4" s="20"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -862,16 +786,18 @@
       <c r="Z4" s="1"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="17"/>
-      <c r="B5" s="18"/>
-      <c r="C5" s="3" t="s">
-        <v>3</v>
+      <c r="A5" s="22" t="s">
+        <v>1</v>
       </c>
-      <c r="D5" s="19"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="12"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="11"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
@@ -892,18 +818,31 @@
       <c r="Z5" s="1"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="17"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="3" t="s">
+      <c r="A6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="19"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="12"/>
+      <c r="C6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
@@ -922,16 +861,14 @@
       <c r="Z6" s="1"/>
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="17"/>
-      <c r="B7" s="18"/>
-      <c r="C7" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" s="19"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="12"/>
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
@@ -952,16 +889,14 @@
       <c r="Z7" s="1"/>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="17"/>
-      <c r="B8" s="18"/>
-      <c r="C8" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" s="19"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="12"/>
+      <c r="A8" s="23"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="11"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
@@ -982,16 +917,16 @@
       <c r="Z8" s="1"/>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="17"/>
-      <c r="B9" s="18"/>
-      <c r="C9" s="3" t="s">
-        <v>7</v>
+      <c r="A9" s="31"/>
+      <c r="B9" s="31"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="32"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="31"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="32" t="s">
+        <v>21</v>
       </c>
-      <c r="D9" s="19"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="12"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
@@ -1012,16 +947,14 @@
       <c r="Z9" s="1"/>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="17"/>
-      <c r="B10" s="18"/>
-      <c r="C10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="19"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="12"/>
+      <c r="A10" s="34"/>
+      <c r="B10" s="35"/>
+      <c r="C10" s="35"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="35"/>
+      <c r="G10" s="35"/>
+      <c r="H10" s="36"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
@@ -1042,16 +975,14 @@
       <c r="Z10" s="1"/>
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="17"/>
-      <c r="B11" s="18"/>
-      <c r="C11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="20"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="21"/>
-      <c r="G11" s="21"/>
-      <c r="H11" s="22"/>
+      <c r="A11" s="34"/>
+      <c r="B11" s="35"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="36"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="35"/>
+      <c r="G11" s="35"/>
+      <c r="H11" s="36"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
@@ -1072,14 +1003,14 @@
       <c r="Z11" s="1"/>
     </row>
     <row r="12" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="23"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
+      <c r="A12" s="34"/>
+      <c r="B12" s="35"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="35"/>
+      <c r="G12" s="35"/>
+      <c r="H12" s="36"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
@@ -1100,18 +1031,14 @@
       <c r="Z12" s="1"/>
     </row>
     <row r="13" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B13" s="21"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="22"/>
+      <c r="A13" s="34"/>
+      <c r="B13" s="35"/>
+      <c r="C13" s="35"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="35"/>
+      <c r="G13" s="35"/>
+      <c r="H13" s="36"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
@@ -1132,30 +1059,14 @@
       <c r="Z13" s="1"/>
     </row>
     <row r="14" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
-      </c>
+      <c r="A14" s="34"/>
+      <c r="B14" s="35"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="35"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="36"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
@@ -1176,14 +1087,14 @@
       <c r="Z14" s="1"/>
     </row>
     <row r="15" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
+      <c r="A15" s="34"/>
+      <c r="B15" s="35"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="35"/>
+      <c r="G15" s="35"/>
+      <c r="H15" s="36"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
@@ -1204,14 +1115,14 @@
       <c r="Z15" s="1"/>
     </row>
     <row r="16" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="25"/>
-      <c r="B16" s="21"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="21"/>
-      <c r="H16" s="22"/>
+      <c r="A16" s="34"/>
+      <c r="B16" s="35"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="35"/>
+      <c r="G16" s="35"/>
+      <c r="H16" s="36"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
@@ -1232,14 +1143,14 @@
       <c r="Z16" s="1"/>
     </row>
     <row r="17" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="33"/>
-      <c r="B17" s="34"/>
-      <c r="C17" s="34"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="34"/>
-      <c r="G17" s="34"/>
-      <c r="H17" s="35"/>
+      <c r="A17" s="34"/>
+      <c r="B17" s="35"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="35"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="36"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
@@ -1260,14 +1171,14 @@
       <c r="Z17" s="1"/>
     </row>
     <row r="18" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="36"/>
-      <c r="B18" s="37"/>
-      <c r="C18" s="37"/>
-      <c r="D18" s="38"/>
-      <c r="E18" s="36"/>
-      <c r="F18" s="37"/>
-      <c r="G18" s="37"/>
-      <c r="H18" s="38"/>
+      <c r="A18" s="34"/>
+      <c r="B18" s="35"/>
+      <c r="C18" s="35"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="35"/>
+      <c r="G18" s="35"/>
+      <c r="H18" s="36"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
@@ -1288,14 +1199,14 @@
       <c r="Z18" s="1"/>
     </row>
     <row r="19" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="36"/>
-      <c r="B19" s="37"/>
-      <c r="C19" s="37"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="36"/>
-      <c r="F19" s="37"/>
-      <c r="G19" s="37"/>
-      <c r="H19" s="38"/>
+      <c r="A19" s="34"/>
+      <c r="B19" s="35"/>
+      <c r="C19" s="35"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="35"/>
+      <c r="G19" s="35"/>
+      <c r="H19" s="36"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
@@ -1316,14 +1227,14 @@
       <c r="Z19" s="1"/>
     </row>
     <row r="20" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="36"/>
-      <c r="B20" s="37"/>
-      <c r="C20" s="37"/>
-      <c r="D20" s="38"/>
-      <c r="E20" s="36"/>
-      <c r="F20" s="37"/>
-      <c r="G20" s="37"/>
-      <c r="H20" s="38"/>
+      <c r="A20" s="37"/>
+      <c r="B20" s="38"/>
+      <c r="C20" s="38"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="37"/>
+      <c r="F20" s="38"/>
+      <c r="G20" s="38"/>
+      <c r="H20" s="39"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
@@ -1344,14 +1255,18 @@
       <c r="Z20" s="1"/>
     </row>
     <row r="21" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="36"/>
-      <c r="B21" s="37"/>
-      <c r="C21" s="37"/>
-      <c r="D21" s="38"/>
-      <c r="E21" s="36"/>
-      <c r="F21" s="37"/>
-      <c r="G21" s="37"/>
-      <c r="H21" s="38"/>
+      <c r="A21" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="F21" s="10"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="11"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
@@ -1372,14 +1287,16 @@
       <c r="Z21" s="1"/>
     </row>
     <row r="22" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="36"/>
-      <c r="B22" s="37"/>
-      <c r="C22" s="37"/>
-      <c r="D22" s="38"/>
-      <c r="E22" s="36"/>
-      <c r="F22" s="37"/>
-      <c r="G22" s="37"/>
-      <c r="H22" s="38"/>
+      <c r="A22" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" s="10"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="11"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
@@ -1400,14 +1317,20 @@
       <c r="Z22" s="1"/>
     </row>
     <row r="23" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="36"/>
-      <c r="B23" s="37"/>
-      <c r="C23" s="37"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="37"/>
-      <c r="G23" s="37"/>
-      <c r="H23" s="38"/>
+      <c r="A23" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="4" t="s">
+        <v>11</v>
+      </c>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
@@ -1428,14 +1351,18 @@
       <c r="Z23" s="1"/>
     </row>
     <row r="24" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="36"/>
-      <c r="B24" s="37"/>
-      <c r="C24" s="37"/>
-      <c r="D24" s="38"/>
-      <c r="E24" s="36"/>
-      <c r="F24" s="37"/>
-      <c r="G24" s="37"/>
-      <c r="H24" s="38"/>
+      <c r="A24" s="5">
+        <v>1</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="5"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
@@ -1456,14 +1383,18 @@
       <c r="Z24" s="1"/>
     </row>
     <row r="25" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="36"/>
-      <c r="B25" s="37"/>
-      <c r="C25" s="37"/>
-      <c r="D25" s="38"/>
-      <c r="E25" s="36"/>
-      <c r="F25" s="37"/>
-      <c r="G25" s="37"/>
-      <c r="H25" s="38"/>
+      <c r="A25" s="5">
+        <v>2</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="5"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
@@ -1484,14 +1415,18 @@
       <c r="Z25" s="1"/>
     </row>
     <row r="26" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="36"/>
-      <c r="B26" s="37"/>
-      <c r="C26" s="37"/>
-      <c r="D26" s="38"/>
-      <c r="E26" s="36"/>
-      <c r="F26" s="37"/>
-      <c r="G26" s="37"/>
-      <c r="H26" s="38"/>
+      <c r="A26" s="5">
+        <v>3</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="10"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="5"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
@@ -1512,14 +1447,18 @@
       <c r="Z26" s="1"/>
     </row>
     <row r="27" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="36"/>
-      <c r="B27" s="37"/>
-      <c r="C27" s="37"/>
-      <c r="D27" s="38"/>
-      <c r="E27" s="36"/>
-      <c r="F27" s="37"/>
-      <c r="G27" s="37"/>
-      <c r="H27" s="38"/>
+      <c r="A27" s="5">
+        <v>4</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" s="10"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="10"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="5"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
@@ -1540,14 +1479,18 @@
       <c r="Z27" s="1"/>
     </row>
     <row r="28" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="39"/>
-      <c r="B28" s="40"/>
-      <c r="C28" s="40"/>
-      <c r="D28" s="41"/>
-      <c r="E28" s="39"/>
-      <c r="F28" s="40"/>
-      <c r="G28" s="40"/>
-      <c r="H28" s="41"/>
+      <c r="A28" s="5">
+        <v>5</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" s="10"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="5"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
@@ -1568,18 +1511,18 @@
       <c r="Z28" s="1"/>
     </row>
     <row r="29" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="26" t="s">
-        <v>15</v>
+      <c r="A29" s="5">
+        <v>6</v>
       </c>
-      <c r="B29" s="21"/>
-      <c r="C29" s="21"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="26" t="s">
-        <v>16</v>
+      <c r="B29" s="9" t="s">
+        <v>17</v>
       </c>
-      <c r="F29" s="21"/>
-      <c r="G29" s="21"/>
-      <c r="H29" s="22"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="5"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
@@ -1600,16 +1543,18 @@
       <c r="Z29" s="1"/>
     </row>
     <row r="30" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="27" t="s">
-        <v>17</v>
+      <c r="A30" s="5">
+        <v>7</v>
       </c>
-      <c r="B30" s="21"/>
-      <c r="C30" s="21"/>
-      <c r="D30" s="21"/>
-      <c r="E30" s="21"/>
-      <c r="F30" s="21"/>
-      <c r="G30" s="21"/>
-      <c r="H30" s="22"/>
+      <c r="B30" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="10"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="5"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
@@ -1629,21 +1574,17 @@
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
     </row>
-    <row r="31" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B31" s="28" t="s">
+    <row r="31" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C31" s="21"/>
-      <c r="D31" s="21"/>
-      <c r="E31" s="21"/>
-      <c r="F31" s="21"/>
-      <c r="G31" s="22"/>
-      <c r="H31" s="5" t="s">
-        <v>20</v>
-      </c>
+      <c r="B31" s="13"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13"/>
+      <c r="G31" s="13"/>
+      <c r="H31" s="14"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
@@ -1663,19 +1604,15 @@
       <c r="Y31" s="1"/>
       <c r="Z31" s="1"/>
     </row>
-    <row r="32" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="6">
-        <v>1</v>
-      </c>
-      <c r="B32" s="29" t="s">
-        <v>21</v>
-      </c>
-      <c r="C32" s="21"/>
-      <c r="D32" s="21"/>
-      <c r="E32" s="21"/>
-      <c r="F32" s="21"/>
-      <c r="G32" s="22"/>
-      <c r="H32" s="6"/>
+    <row r="32" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="15"/>
+      <c r="B32" s="13"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+      <c r="H32" s="14"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
@@ -1695,19 +1632,15 @@
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
     </row>
-    <row r="33" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="6">
-        <v>2</v>
-      </c>
-      <c r="B33" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="C33" s="21"/>
-      <c r="D33" s="21"/>
-      <c r="E33" s="21"/>
-      <c r="F33" s="21"/>
-      <c r="G33" s="22"/>
-      <c r="H33" s="6"/>
+    <row r="33" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="16"/>
+      <c r="B33" s="10"/>
+      <c r="C33" s="10"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="10"/>
+      <c r="G33" s="10"/>
+      <c r="H33" s="11"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
@@ -1727,19 +1660,15 @@
       <c r="Y33" s="1"/>
       <c r="Z33" s="1"/>
     </row>
-    <row r="34" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="6">
-        <v>3</v>
-      </c>
-      <c r="B34" s="29" t="s">
-        <v>23</v>
-      </c>
-      <c r="C34" s="21"/>
-      <c r="D34" s="21"/>
-      <c r="E34" s="21"/>
-      <c r="F34" s="21"/>
-      <c r="G34" s="22"/>
-      <c r="H34" s="6"/>
+    <row r="34" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="6"/>
+      <c r="B34" s="7"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="7"/>
+      <c r="H34" s="8"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
@@ -1759,19 +1688,15 @@
       <c r="Y34" s="1"/>
       <c r="Z34" s="1"/>
     </row>
-    <row r="35" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="6">
-        <v>4</v>
-      </c>
-      <c r="B35" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="C35" s="21"/>
-      <c r="D35" s="21"/>
-      <c r="E35" s="21"/>
-      <c r="F35" s="21"/>
-      <c r="G35" s="22"/>
-      <c r="H35" s="6"/>
+    <row r="35" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="16"/>
+      <c r="B35" s="10"/>
+      <c r="C35" s="10"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="10"/>
+      <c r="F35" s="10"/>
+      <c r="G35" s="10"/>
+      <c r="H35" s="11"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
@@ -1791,19 +1716,15 @@
       <c r="Y35" s="1"/>
       <c r="Z35" s="1"/>
     </row>
-    <row r="36" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="6">
-        <v>5</v>
-      </c>
-      <c r="B36" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="C36" s="21"/>
-      <c r="D36" s="21"/>
-      <c r="E36" s="21"/>
-      <c r="F36" s="21"/>
-      <c r="G36" s="22"/>
-      <c r="H36" s="6"/>
+    <row r="36" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="16"/>
+      <c r="B36" s="10"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="10"/>
+      <c r="F36" s="10"/>
+      <c r="G36" s="10"/>
+      <c r="H36" s="11"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
@@ -1823,19 +1744,15 @@
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
     </row>
-    <row r="37" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="6">
-        <v>6</v>
-      </c>
-      <c r="B37" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="C37" s="21"/>
-      <c r="D37" s="21"/>
-      <c r="E37" s="21"/>
-      <c r="F37" s="21"/>
-      <c r="G37" s="22"/>
-      <c r="H37" s="6"/>
+    <row r="37" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="1"/>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
@@ -1855,19 +1772,15 @@
       <c r="Y37" s="1"/>
       <c r="Z37" s="1"/>
     </row>
-    <row r="38" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="6">
-        <v>7</v>
-      </c>
-      <c r="B38" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="C38" s="21"/>
-      <c r="D38" s="21"/>
-      <c r="E38" s="21"/>
-      <c r="F38" s="21"/>
-      <c r="G38" s="22"/>
-      <c r="H38" s="6"/>
+    <row r="38" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="1"/>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
@@ -1888,16 +1801,14 @@
       <c r="Z38" s="1"/>
     </row>
     <row r="39" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="30" t="s">
-        <v>28</v>
-      </c>
-      <c r="B39" s="11"/>
-      <c r="C39" s="11"/>
-      <c r="D39" s="11"/>
-      <c r="E39" s="11"/>
-      <c r="F39" s="11"/>
-      <c r="G39" s="11"/>
-      <c r="H39" s="12"/>
+      <c r="A39" s="1"/>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
@@ -1918,14 +1829,14 @@
       <c r="Z39" s="1"/>
     </row>
     <row r="40" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="31"/>
-      <c r="B40" s="11"/>
-      <c r="C40" s="11"/>
-      <c r="D40" s="11"/>
-      <c r="E40" s="11"/>
-      <c r="F40" s="11"/>
-      <c r="G40" s="11"/>
-      <c r="H40" s="12"/>
+      <c r="A40" s="1"/>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
@@ -1946,14 +1857,14 @@
       <c r="Z40" s="1"/>
     </row>
     <row r="41" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="32"/>
-      <c r="B41" s="21"/>
-      <c r="C41" s="21"/>
-      <c r="D41" s="21"/>
-      <c r="E41" s="21"/>
-      <c r="F41" s="21"/>
-      <c r="G41" s="21"/>
-      <c r="H41" s="22"/>
+      <c r="A41" s="1"/>
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
@@ -1974,14 +1885,14 @@
       <c r="Z41" s="1"/>
     </row>
     <row r="42" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="7"/>
-      <c r="B42" s="8"/>
-      <c r="C42" s="8"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="8"/>
-      <c r="G42" s="8"/>
-      <c r="H42" s="9"/>
+      <c r="A42" s="1"/>
+      <c r="B42" s="1"/>
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
@@ -2002,14 +1913,14 @@
       <c r="Z42" s="1"/>
     </row>
     <row r="43" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="32"/>
-      <c r="B43" s="21"/>
-      <c r="C43" s="21"/>
-      <c r="D43" s="21"/>
-      <c r="E43" s="21"/>
-      <c r="F43" s="21"/>
-      <c r="G43" s="21"/>
-      <c r="H43" s="22"/>
+      <c r="A43" s="1"/>
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
@@ -5697,266 +5608,33 @@
       <c r="Y174" s="1"/>
       <c r="Z174" s="1"/>
     </row>
-    <row r="175" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A175" s="1"/>
-      <c r="B175" s="1"/>
-      <c r="C175" s="1"/>
-      <c r="D175" s="1"/>
-      <c r="E175" s="1"/>
-      <c r="F175" s="1"/>
-      <c r="G175" s="1"/>
-      <c r="H175" s="1"/>
-      <c r="I175" s="1"/>
-      <c r="J175" s="1"/>
-      <c r="K175" s="1"/>
-      <c r="L175" s="1"/>
-      <c r="M175" s="1"/>
-      <c r="N175" s="1"/>
-      <c r="O175" s="1"/>
-      <c r="P175" s="1"/>
-      <c r="Q175" s="1"/>
-      <c r="R175" s="1"/>
-      <c r="S175" s="1"/>
-      <c r="T175" s="1"/>
-      <c r="U175" s="1"/>
-      <c r="V175" s="1"/>
-      <c r="W175" s="1"/>
-      <c r="X175" s="1"/>
-      <c r="Y175" s="1"/>
-      <c r="Z175" s="1"/>
-    </row>
-    <row r="176" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A176" s="1"/>
-      <c r="B176" s="1"/>
-      <c r="C176" s="1"/>
-      <c r="D176" s="1"/>
-      <c r="E176" s="1"/>
-      <c r="F176" s="1"/>
-      <c r="G176" s="1"/>
-      <c r="H176" s="1"/>
-      <c r="I176" s="1"/>
-      <c r="J176" s="1"/>
-      <c r="K176" s="1"/>
-      <c r="L176" s="1"/>
-      <c r="M176" s="1"/>
-      <c r="N176" s="1"/>
-      <c r="O176" s="1"/>
-      <c r="P176" s="1"/>
-      <c r="Q176" s="1"/>
-      <c r="R176" s="1"/>
-      <c r="S176" s="1"/>
-      <c r="T176" s="1"/>
-      <c r="U176" s="1"/>
-      <c r="V176" s="1"/>
-      <c r="W176" s="1"/>
-      <c r="X176" s="1"/>
-      <c r="Y176" s="1"/>
-      <c r="Z176" s="1"/>
-    </row>
-    <row r="177" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A177" s="1"/>
-      <c r="B177" s="1"/>
-      <c r="C177" s="1"/>
-      <c r="D177" s="1"/>
-      <c r="E177" s="1"/>
-      <c r="F177" s="1"/>
-      <c r="G177" s="1"/>
-      <c r="H177" s="1"/>
-      <c r="I177" s="1"/>
-      <c r="J177" s="1"/>
-      <c r="K177" s="1"/>
-      <c r="L177" s="1"/>
-      <c r="M177" s="1"/>
-      <c r="N177" s="1"/>
-      <c r="O177" s="1"/>
-      <c r="P177" s="1"/>
-      <c r="Q177" s="1"/>
-      <c r="R177" s="1"/>
-      <c r="S177" s="1"/>
-      <c r="T177" s="1"/>
-      <c r="U177" s="1"/>
-      <c r="V177" s="1"/>
-      <c r="W177" s="1"/>
-      <c r="X177" s="1"/>
-      <c r="Y177" s="1"/>
-      <c r="Z177" s="1"/>
-    </row>
-    <row r="178" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A178" s="1"/>
-      <c r="B178" s="1"/>
-      <c r="C178" s="1"/>
-      <c r="D178" s="1"/>
-      <c r="E178" s="1"/>
-      <c r="F178" s="1"/>
-      <c r="G178" s="1"/>
-      <c r="H178" s="1"/>
-      <c r="I178" s="1"/>
-      <c r="J178" s="1"/>
-      <c r="K178" s="1"/>
-      <c r="L178" s="1"/>
-      <c r="M178" s="1"/>
-      <c r="N178" s="1"/>
-      <c r="O178" s="1"/>
-      <c r="P178" s="1"/>
-      <c r="Q178" s="1"/>
-      <c r="R178" s="1"/>
-      <c r="S178" s="1"/>
-      <c r="T178" s="1"/>
-      <c r="U178" s="1"/>
-      <c r="V178" s="1"/>
-      <c r="W178" s="1"/>
-      <c r="X178" s="1"/>
-      <c r="Y178" s="1"/>
-      <c r="Z178" s="1"/>
-    </row>
-    <row r="179" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A179" s="1"/>
-      <c r="B179" s="1"/>
-      <c r="C179" s="1"/>
-      <c r="D179" s="1"/>
-      <c r="E179" s="1"/>
-      <c r="F179" s="1"/>
-      <c r="G179" s="1"/>
-      <c r="H179" s="1"/>
-      <c r="I179" s="1"/>
-      <c r="J179" s="1"/>
-      <c r="K179" s="1"/>
-      <c r="L179" s="1"/>
-      <c r="M179" s="1"/>
-      <c r="N179" s="1"/>
-      <c r="O179" s="1"/>
-      <c r="P179" s="1"/>
-      <c r="Q179" s="1"/>
-      <c r="R179" s="1"/>
-      <c r="S179" s="1"/>
-      <c r="T179" s="1"/>
-      <c r="U179" s="1"/>
-      <c r="V179" s="1"/>
-      <c r="W179" s="1"/>
-      <c r="X179" s="1"/>
-      <c r="Y179" s="1"/>
-      <c r="Z179" s="1"/>
-    </row>
-    <row r="180" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="1"/>
-      <c r="B180" s="1"/>
-      <c r="C180" s="1"/>
-      <c r="D180" s="1"/>
-      <c r="E180" s="1"/>
-      <c r="F180" s="1"/>
-      <c r="G180" s="1"/>
-      <c r="H180" s="1"/>
-      <c r="I180" s="1"/>
-      <c r="J180" s="1"/>
-      <c r="K180" s="1"/>
-      <c r="L180" s="1"/>
-      <c r="M180" s="1"/>
-      <c r="N180" s="1"/>
-      <c r="O180" s="1"/>
-      <c r="P180" s="1"/>
-      <c r="Q180" s="1"/>
-      <c r="R180" s="1"/>
-      <c r="S180" s="1"/>
-      <c r="T180" s="1"/>
-      <c r="U180" s="1"/>
-      <c r="V180" s="1"/>
-      <c r="W180" s="1"/>
-      <c r="X180" s="1"/>
-      <c r="Y180" s="1"/>
-      <c r="Z180" s="1"/>
-    </row>
-    <row r="181" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A181" s="1"/>
-      <c r="B181" s="1"/>
-      <c r="C181" s="1"/>
-      <c r="D181" s="1"/>
-      <c r="E181" s="1"/>
-      <c r="F181" s="1"/>
-      <c r="G181" s="1"/>
-      <c r="H181" s="1"/>
-      <c r="I181" s="1"/>
-      <c r="J181" s="1"/>
-      <c r="K181" s="1"/>
-      <c r="L181" s="1"/>
-      <c r="M181" s="1"/>
-      <c r="N181" s="1"/>
-      <c r="O181" s="1"/>
-      <c r="P181" s="1"/>
-      <c r="Q181" s="1"/>
-      <c r="R181" s="1"/>
-      <c r="S181" s="1"/>
-      <c r="T181" s="1"/>
-      <c r="U181" s="1"/>
-      <c r="V181" s="1"/>
-      <c r="W181" s="1"/>
-      <c r="X181" s="1"/>
-      <c r="Y181" s="1"/>
-      <c r="Z181" s="1"/>
-    </row>
-    <row r="182" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A182" s="1"/>
-      <c r="B182" s="1"/>
-      <c r="C182" s="1"/>
-      <c r="D182" s="1"/>
-      <c r="E182" s="1"/>
-      <c r="F182" s="1"/>
-      <c r="G182" s="1"/>
-      <c r="H182" s="1"/>
-      <c r="I182" s="1"/>
-      <c r="J182" s="1"/>
-      <c r="K182" s="1"/>
-      <c r="L182" s="1"/>
-      <c r="M182" s="1"/>
-      <c r="N182" s="1"/>
-      <c r="O182" s="1"/>
-      <c r="P182" s="1"/>
-      <c r="Q182" s="1"/>
-      <c r="R182" s="1"/>
-      <c r="S182" s="1"/>
-      <c r="T182" s="1"/>
-      <c r="U182" s="1"/>
-      <c r="V182" s="1"/>
-      <c r="W182" s="1"/>
-      <c r="X182" s="1"/>
-      <c r="Y182" s="1"/>
-      <c r="Z182" s="1"/>
-    </row>
   </sheetData>
-  <mergeCells count="30">
-    <mergeCell ref="B38:G38"/>
-    <mergeCell ref="A39:H39"/>
-    <mergeCell ref="A40:H40"/>
-    <mergeCell ref="A41:H41"/>
-    <mergeCell ref="A43:H43"/>
-    <mergeCell ref="B33:G33"/>
-    <mergeCell ref="B34:G34"/>
-    <mergeCell ref="B35:G35"/>
-    <mergeCell ref="B36:G36"/>
-    <mergeCell ref="B37:G37"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="E29:H29"/>
-    <mergeCell ref="A30:H30"/>
-    <mergeCell ref="B31:G31"/>
-    <mergeCell ref="B32:G32"/>
-    <mergeCell ref="A12:H12"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="E13:H13"/>
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="A1:H2"/>
-    <mergeCell ref="A3:B11"/>
-    <mergeCell ref="D3:H3"/>
-    <mergeCell ref="D4:H4"/>
-    <mergeCell ref="D5:H5"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="D9:H9"/>
-    <mergeCell ref="D10:H10"/>
-    <mergeCell ref="D11:H11"/>
+  <mergeCells count="22">
+    <mergeCell ref="A2:H3"/>
+    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="E21:H21"/>
+    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="B24:G24"/>
+    <mergeCell ref="B25:G25"/>
+    <mergeCell ref="B26:G26"/>
+    <mergeCell ref="B27:G27"/>
+    <mergeCell ref="B28:G28"/>
+    <mergeCell ref="B29:G29"/>
+    <mergeCell ref="B30:G30"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A32:H32"/>
+    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="A35:H35"/>
   </mergeCells>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="14" pageOrder="overThenDown" orientation="portrait" cellComments="atEnd"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/public/informes-templates/INFORME ADICIONAL  .xlsx
+++ b/public/informes-templates/INFORME ADICIONAL  .xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{514FD4D7-833F-4AA4-80C5-64B7042E906B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA689243-ED69-46E0-B646-D0390B20FBC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -87,7 +87,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -145,6 +145,12 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="7">
@@ -329,7 +335,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -345,81 +351,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -447,6 +378,78 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -673,16 +676,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="14"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="20"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -703,14 +706,14 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="26"/>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="28"/>
+      <c r="A2" s="31"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="33"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -731,14 +734,14 @@
       <c r="Z2" s="1"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="25"/>
-      <c r="B3" s="29"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="30"/>
+      <c r="A3" s="34"/>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="36"/>
       <c r="I3" s="1"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
@@ -758,14 +761,14 @@
       <c r="Z3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="20"/>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
+      <c r="A4" s="24"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -786,18 +789,18 @@
       <c r="Z4" s="1"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="22" t="s">
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="11"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="17"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
@@ -889,14 +892,14 @@
       <c r="Z7" s="1"/>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="23"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="11"/>
+      <c r="A8" s="27"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="17"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
@@ -917,14 +920,14 @@
       <c r="Z8" s="1"/>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="32"/>
-      <c r="E9" s="33"/>
-      <c r="F9" s="31"/>
-      <c r="G9" s="31"/>
-      <c r="H9" s="32" t="s">
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="7" t="s">
         <v>21</v>
       </c>
       <c r="I9" s="1"/>
@@ -947,14 +950,14 @@
       <c r="Z9" s="1"/>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="34"/>
-      <c r="B10" s="35"/>
-      <c r="C10" s="35"/>
-      <c r="D10" s="36"/>
-      <c r="E10" s="34"/>
-      <c r="F10" s="35"/>
-      <c r="G10" s="35"/>
-      <c r="H10" s="36"/>
+      <c r="A10" s="9"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="11"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
@@ -975,14 +978,14 @@
       <c r="Z10" s="1"/>
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="34"/>
-      <c r="B11" s="35"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="36"/>
-      <c r="E11" s="34"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="35"/>
-      <c r="H11" s="36"/>
+      <c r="A11" s="9"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="11"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
@@ -1003,14 +1006,14 @@
       <c r="Z11" s="1"/>
     </row>
     <row r="12" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="34"/>
-      <c r="B12" s="35"/>
-      <c r="C12" s="35"/>
-      <c r="D12" s="36"/>
-      <c r="E12" s="34"/>
-      <c r="F12" s="35"/>
-      <c r="G12" s="35"/>
-      <c r="H12" s="36"/>
+      <c r="A12" s="9"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="11"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
@@ -1031,14 +1034,14 @@
       <c r="Z12" s="1"/>
     </row>
     <row r="13" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="34"/>
-      <c r="B13" s="35"/>
-      <c r="C13" s="35"/>
-      <c r="D13" s="36"/>
-      <c r="E13" s="34"/>
-      <c r="F13" s="35"/>
-      <c r="G13" s="35"/>
-      <c r="H13" s="36"/>
+      <c r="A13" s="9"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="11"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
@@ -1059,14 +1062,14 @@
       <c r="Z13" s="1"/>
     </row>
     <row r="14" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="34"/>
-      <c r="B14" s="35"/>
-      <c r="C14" s="35"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="34"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="36"/>
+      <c r="A14" s="9"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="11"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
@@ -1087,14 +1090,14 @@
       <c r="Z14" s="1"/>
     </row>
     <row r="15" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="34"/>
-      <c r="B15" s="35"/>
-      <c r="C15" s="35"/>
-      <c r="D15" s="36"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="35"/>
-      <c r="G15" s="35"/>
-      <c r="H15" s="36"/>
+      <c r="A15" s="9"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="11"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
@@ -1115,14 +1118,14 @@
       <c r="Z15" s="1"/>
     </row>
     <row r="16" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="34"/>
-      <c r="B16" s="35"/>
-      <c r="C16" s="35"/>
-      <c r="D16" s="36"/>
-      <c r="E16" s="34"/>
-      <c r="F16" s="35"/>
-      <c r="G16" s="35"/>
-      <c r="H16" s="36"/>
+      <c r="A16" s="9"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="11"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
@@ -1143,14 +1146,14 @@
       <c r="Z16" s="1"/>
     </row>
     <row r="17" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="34"/>
-      <c r="B17" s="35"/>
-      <c r="C17" s="35"/>
-      <c r="D17" s="36"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="35"/>
-      <c r="H17" s="36"/>
+      <c r="A17" s="9"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="11"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
@@ -1171,14 +1174,14 @@
       <c r="Z17" s="1"/>
     </row>
     <row r="18" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="34"/>
-      <c r="B18" s="35"/>
-      <c r="C18" s="35"/>
-      <c r="D18" s="36"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="35"/>
-      <c r="H18" s="36"/>
+      <c r="A18" s="9"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="11"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
@@ -1199,14 +1202,14 @@
       <c r="Z18" s="1"/>
     </row>
     <row r="19" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="34"/>
-      <c r="B19" s="35"/>
-      <c r="C19" s="35"/>
-      <c r="D19" s="36"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="35"/>
-      <c r="G19" s="35"/>
-      <c r="H19" s="36"/>
+      <c r="A19" s="9"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="11"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
@@ -1227,14 +1230,14 @@
       <c r="Z19" s="1"/>
     </row>
     <row r="20" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="37"/>
-      <c r="B20" s="38"/>
-      <c r="C20" s="38"/>
-      <c r="D20" s="39"/>
-      <c r="E20" s="37"/>
-      <c r="F20" s="38"/>
-      <c r="G20" s="38"/>
-      <c r="H20" s="39"/>
+      <c r="A20" s="12"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="14"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
@@ -1255,18 +1258,18 @@
       <c r="Z20" s="1"/>
     </row>
     <row r="21" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="17" t="s">
+      <c r="B21" s="16"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="11"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="16"/>
+      <c r="H21" s="17"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
@@ -1287,16 +1290,16 @@
       <c r="Z21" s="1"/>
     </row>
     <row r="22" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="18" t="s">
+      <c r="A22" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="11"/>
+      <c r="B22" s="16"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="17"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
@@ -1320,14 +1323,14 @@
       <c r="A23" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B23" s="19" t="s">
+      <c r="B23" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="11"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="17"/>
       <c r="H23" s="4" t="s">
         <v>11</v>
       </c>
@@ -1354,14 +1357,14 @@
       <c r="A24" s="5">
         <v>1</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="11"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="17"/>
       <c r="H24" s="5"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
@@ -1386,14 +1389,14 @@
       <c r="A25" s="5">
         <v>2</v>
       </c>
-      <c r="B25" s="9" t="s">
+      <c r="B25" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="11"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="17"/>
       <c r="H25" s="5"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
@@ -1418,14 +1421,14 @@
       <c r="A26" s="5">
         <v>3</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="B26" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="11"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="17"/>
       <c r="H26" s="5"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
@@ -1450,14 +1453,14 @@
       <c r="A27" s="5">
         <v>4</v>
       </c>
-      <c r="B27" s="9" t="s">
+      <c r="B27" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="C27" s="10"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="10"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="11"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="17"/>
       <c r="H27" s="5"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
@@ -1482,14 +1485,14 @@
       <c r="A28" s="5">
         <v>5</v>
       </c>
-      <c r="B28" s="9" t="s">
+      <c r="B28" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="11"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="17"/>
       <c r="H28" s="5"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
@@ -1514,14 +1517,14 @@
       <c r="A29" s="5">
         <v>6</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="B29" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="C29" s="10"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="10"/>
-      <c r="F29" s="10"/>
-      <c r="G29" s="11"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="17"/>
       <c r="H29" s="5"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
@@ -1546,14 +1549,14 @@
       <c r="A30" s="5">
         <v>7</v>
       </c>
-      <c r="B30" s="9" t="s">
+      <c r="B30" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="10"/>
-      <c r="G30" s="11"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="17"/>
       <c r="H30" s="5"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
@@ -1575,16 +1578,16 @@
       <c r="Z30" s="1"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="12" t="s">
+      <c r="A31" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="B31" s="13"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
-      <c r="G31" s="13"/>
-      <c r="H31" s="14"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="20"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
@@ -1605,14 +1608,14 @@
       <c r="Z31" s="1"/>
     </row>
     <row r="32" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="15"/>
-      <c r="B32" s="13"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="14"/>
+      <c r="A32" s="30"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="20"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
@@ -1633,14 +1636,14 @@
       <c r="Z32" s="1"/>
     </row>
     <row r="33" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="16"/>
-      <c r="B33" s="10"/>
-      <c r="C33" s="10"/>
-      <c r="D33" s="10"/>
-      <c r="E33" s="10"/>
-      <c r="F33" s="10"/>
-      <c r="G33" s="10"/>
-      <c r="H33" s="11"/>
+      <c r="A33" s="15"/>
+      <c r="B33" s="16"/>
+      <c r="C33" s="16"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="16"/>
+      <c r="H33" s="17"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
@@ -1661,14 +1664,14 @@
       <c r="Z33" s="1"/>
     </row>
     <row r="34" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="6"/>
-      <c r="B34" s="7"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
-      <c r="G34" s="7"/>
-      <c r="H34" s="8"/>
+      <c r="A34" s="37"/>
+      <c r="B34" s="37"/>
+      <c r="C34" s="37"/>
+      <c r="D34" s="37"/>
+      <c r="E34" s="37"/>
+      <c r="F34" s="37"/>
+      <c r="G34" s="37"/>
+      <c r="H34" s="38"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
@@ -1689,14 +1692,14 @@
       <c r="Z34" s="1"/>
     </row>
     <row r="35" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="16"/>
-      <c r="B35" s="10"/>
-      <c r="C35" s="10"/>
-      <c r="D35" s="10"/>
-      <c r="E35" s="10"/>
-      <c r="F35" s="10"/>
-      <c r="G35" s="10"/>
-      <c r="H35" s="11"/>
+      <c r="A35" s="15"/>
+      <c r="B35" s="16"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="16"/>
+      <c r="H35" s="17"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
@@ -1717,14 +1720,14 @@
       <c r="Z35" s="1"/>
     </row>
     <row r="36" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="16"/>
-      <c r="B36" s="10"/>
-      <c r="C36" s="10"/>
-      <c r="D36" s="10"/>
-      <c r="E36" s="10"/>
-      <c r="F36" s="10"/>
-      <c r="G36" s="10"/>
-      <c r="H36" s="11"/>
+      <c r="A36" s="15"/>
+      <c r="B36" s="16"/>
+      <c r="C36" s="16"/>
+      <c r="D36" s="16"/>
+      <c r="E36" s="16"/>
+      <c r="F36" s="16"/>
+      <c r="G36" s="16"/>
+      <c r="H36" s="17"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
@@ -5609,18 +5612,12 @@
       <c r="Z174" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
-    <mergeCell ref="A2:H3"/>
+  <mergeCells count="23">
     <mergeCell ref="A36:H36"/>
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="E5:H5"/>
     <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="E21:H21"/>
-    <mergeCell ref="A22:H22"/>
-    <mergeCell ref="B23:G23"/>
     <mergeCell ref="B24:G24"/>
     <mergeCell ref="B25:G25"/>
     <mergeCell ref="B26:G26"/>
@@ -5632,6 +5629,13 @@
     <mergeCell ref="A32:H32"/>
     <mergeCell ref="A33:H33"/>
     <mergeCell ref="A35:H35"/>
+    <mergeCell ref="A34:H34"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="E21:H21"/>
+    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="A2:H3"/>
   </mergeCells>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
